--- a/data/image_metadata.xlsx
+++ b/data/image_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Hamed\Image Captioning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338DB49A-A5F1-4382-A05B-1CAB96925F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3709001C-46BB-4B6A-87EE-6D28A53D2F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44835" yWindow="195" windowWidth="27900" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="120" windowWidth="27900" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="230">
   <si>
     <t>project_id</t>
   </si>
@@ -472,9 +472,6 @@
     <t>Different sheets of metal with drilled holes, two packaged half-shells, a bag of screws, a bag of nuts, and a bag of washers.</t>
   </si>
   <si>
-    <t>Flange adapter</t>
-  </si>
-  <si>
     <t>Four people are working on the steel frame</t>
   </si>
   <si>
@@ -667,9 +664,6 @@
     <t>Bayonet standing on a table</t>
   </si>
   <si>
-    <t>flange</t>
-  </si>
-  <si>
     <t>Window for visualizing rotation</t>
   </si>
   <si>
@@ -707,6 +701,15 @@
   </si>
   <si>
     <t>Four round parts with a cyntrical hole in the middle made of stainless steel</t>
+  </si>
+  <si>
+    <t>A round turning part made of stainless steel with flange connections on the top and bottom and a groove in the middle of the inside surface</t>
+  </si>
+  <si>
+    <t>A connecting flange with a short protrusion on the top made of stainless steel</t>
+  </si>
+  <si>
+    <t>A connecting flange adapter with a large flange on the bottom side and a smaller flange on the top made of stainless steel. There is a circular centric recess on the top</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1120,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1134,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1148,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1162,7 +1165,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1176,7 +1179,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1190,7 +1193,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1204,7 +1207,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1218,7 +1221,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1232,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1246,7 +1249,7 @@
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1260,7 +1263,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1274,7 +1277,7 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1288,7 +1291,7 @@
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1302,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1316,7 +1319,7 @@
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1330,7 +1333,7 @@
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1344,7 +1347,7 @@
         <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1358,7 +1361,7 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1372,7 +1375,7 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1386,7 +1389,7 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1400,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1414,7 +1417,7 @@
         <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1428,7 +1431,7 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1442,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1456,7 +1459,7 @@
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1470,7 +1473,7 @@
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1484,7 +1487,7 @@
         <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1498,7 +1501,7 @@
         <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1512,7 +1515,7 @@
         <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1526,7 +1529,7 @@
         <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1680,7 +1683,7 @@
         <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1750,7 +1753,7 @@
         <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1862,7 +1865,7 @@
         <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1876,7 +1879,7 @@
         <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1890,7 +1893,7 @@
         <v>63</v>
       </c>
       <c r="D57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1904,7 +1907,7 @@
         <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1918,7 +1921,7 @@
         <v>65</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1932,7 +1935,7 @@
         <v>66</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1946,7 +1949,7 @@
         <v>67</v>
       </c>
       <c r="D61" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1960,7 +1963,7 @@
         <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1974,7 +1977,7 @@
         <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1988,7 +1991,7 @@
         <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2002,7 +2005,7 @@
         <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2016,7 +2019,7 @@
         <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2030,7 +2033,7 @@
         <v>73</v>
       </c>
       <c r="D67" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2044,7 +2047,7 @@
         <v>74</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2058,7 +2061,7 @@
         <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2072,7 +2075,7 @@
         <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2086,7 +2089,7 @@
         <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2100,7 +2103,7 @@
         <v>78</v>
       </c>
       <c r="D72" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2114,7 +2117,7 @@
         <v>79</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2128,7 +2131,7 @@
         <v>80</v>
       </c>
       <c r="D74" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2142,7 +2145,7 @@
         <v>81</v>
       </c>
       <c r="D75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2156,7 +2159,7 @@
         <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2170,7 +2173,7 @@
         <v>83</v>
       </c>
       <c r="D77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2184,7 +2187,7 @@
         <v>84</v>
       </c>
       <c r="D78" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2198,7 +2201,7 @@
         <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2212,7 +2215,7 @@
         <v>86</v>
       </c>
       <c r="D80" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2226,7 +2229,7 @@
         <v>87</v>
       </c>
       <c r="D81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2240,7 +2243,7 @@
         <v>88</v>
       </c>
       <c r="D82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2254,7 +2257,7 @@
         <v>89</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2268,7 +2271,7 @@
         <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2282,7 +2285,7 @@
         <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2296,7 +2299,7 @@
         <v>92</v>
       </c>
       <c r="D86" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2310,7 +2313,7 @@
         <v>93</v>
       </c>
       <c r="D87" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2324,7 +2327,7 @@
         <v>94</v>
       </c>
       <c r="D88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2338,7 +2341,7 @@
         <v>95</v>
       </c>
       <c r="D89" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2352,7 +2355,7 @@
         <v>96</v>
       </c>
       <c r="D90" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2366,7 +2369,7 @@
         <v>97</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2394,7 +2397,7 @@
         <v>99</v>
       </c>
       <c r="D93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2408,7 +2411,7 @@
         <v>100</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2422,7 +2425,7 @@
         <v>101</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2436,7 +2439,7 @@
         <v>102</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2450,7 +2453,7 @@
         <v>103</v>
       </c>
       <c r="D97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2464,7 +2467,7 @@
         <v>104</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2478,7 +2481,7 @@
         <v>105</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2492,7 +2495,7 @@
         <v>106</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2506,7 +2509,7 @@
         <v>107</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2520,7 +2523,7 @@
         <v>108</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2534,7 +2537,7 @@
         <v>109</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2548,7 +2551,7 @@
         <v>110</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2562,7 +2565,7 @@
         <v>111</v>
       </c>
       <c r="D105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2576,7 +2579,7 @@
         <v>112</v>
       </c>
       <c r="D106" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2590,7 +2593,7 @@
         <v>113</v>
       </c>
       <c r="D107" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2604,7 +2607,7 @@
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2618,7 +2621,7 @@
         <v>115</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2632,7 +2635,7 @@
         <v>116</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2646,7 +2649,7 @@
         <v>117</v>
       </c>
       <c r="D111" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2660,7 +2663,7 @@
         <v>118</v>
       </c>
       <c r="D112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2674,7 +2677,7 @@
         <v>119</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2688,7 +2691,7 @@
         <v>120</v>
       </c>
       <c r="D114" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2702,7 +2705,7 @@
         <v>121</v>
       </c>
       <c r="D115" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2716,7 +2719,7 @@
         <v>122</v>
       </c>
       <c r="D116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2730,7 +2733,7 @@
         <v>123</v>
       </c>
       <c r="D117" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2744,7 +2747,7 @@
         <v>124</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2758,7 +2761,7 @@
         <v>125</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2772,7 +2775,7 @@
         <v>126</v>
       </c>
       <c r="D120" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2786,7 +2789,7 @@
         <v>127</v>
       </c>
       <c r="D121" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
